--- a/main/ig/StructureDefinition-dmi-devicedefinition.xlsx
+++ b/main/ig/StructureDefinition-dmi-devicedefinition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T10:37:28+00:00</t>
+    <t>2026-03-05T09:47:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-devicedefinition.xlsx
+++ b/main/ig/StructureDefinition-dmi-devicedefinition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T09:47:44+00:00</t>
+    <t>2026-03-05T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-devicedefinition.xlsx
+++ b/main/ig/StructureDefinition-dmi-devicedefinition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4223" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4277" uniqueCount="457">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:00:25+00:00</t>
+    <t>2026-03-05T10:01:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -263,7 +263,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
   </si>
   <si>
     <t>Entity. Role, or Act</t>
@@ -310,10 +310,17 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>DeviceDefinition.implicitRules</t>
   </si>
   <si>
@@ -333,6 +340,9 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>DeviceDefinition.language</t>
   </si>
   <si>
@@ -410,26 +420,33 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>DeviceDefinition.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
   </si>
   <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
 </t>
   </si>
   <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
     <t>open</t>
   </si>
   <si>
@@ -456,10 +473,6 @@
     <t>Extension créée dans ce volet pour représenter la classe de risque.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>DeviceDefinition.extension:ReferenceDistributeur</t>
   </si>
   <si>
@@ -495,10 +508,6 @@
     <t>DeviceDefinition.modifierExtension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -506,9 +515,6 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -531,6 +537,9 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
+    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
+  </si>
+  <si>
     <t>DeviceDefinition.udiDeviceIdentifier</t>
   </si>
   <si>
@@ -560,13 +569,7 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>DeviceDefinition.udiDeviceIdentifier.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -601,6 +604,9 @@
     <t>The identifier that is to be associated with every Device that references this DeviceDefintiion for the issuer and jurisdication porvided in the DeviceDefinition.udiDeviceIdentifier.</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>DeviceDefinition.udiDeviceIdentifier.issuer</t>
   </si>
   <si>
@@ -608,6 +614,9 @@
   </si>
   <si>
     <t>The organization that assigns the identifier algorithm.</t>
+  </si>
+  <si>
+    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
   </si>
   <si>
     <t>DeviceDefinition.udiDeviceIdentifier.jurisdiction</t>
@@ -716,6 +725,9 @@
     <t>What kind of device or device system this is.</t>
   </si>
   <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
     <t>example</t>
   </si>
   <si>
@@ -723,6 +735,9 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/device-kind|4.0.1</t>
+  </si>
+  <si>
+    <t>CD</t>
   </si>
   <si>
     <t>DeviceDefinition.specialization</t>
@@ -811,9 +826,6 @@
     <t>DeviceDefinition.physicalCharacteristics.extension</t>
   </si>
   <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
     <t>DeviceDefinition.physicalCharacteristics.extension:InternalDiameter</t>
   </si>
   <si>
@@ -846,7 +858,17 @@
     <t>Where applicable, the height can be specified using a numerical value and its unit of measurement The unit of measurement shall be specified in accordance with ISO 11240 and the resulting terminology The symbol and the symbol identifier shall be used.</t>
   </si>
   <si>
+    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
+  </si>
+  <si>
     <t>ProdCharacteristic.height</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}</t>
+  </si>
+  <si>
+    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
   </si>
   <si>
     <t>DeviceDefinition.physicalCharacteristics.width</t>
@@ -958,7 +980,17 @@
     <t>Where applicable, the image can be provided The format of the image attachment shall be specified by regional implementations.</t>
   </si>
   <si>
+    <t>When providing a summary view (for example with Observation.value[x]) Attachment should be represented with a brief display text such as "Signed Procedure Consent".</t>
+  </si>
+  <si>
     <t>ProdCharacteristic.image</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+att-1:If the Attachment has data, it SHALL have a contentType {data.empty() or contentType.exists()}</t>
+  </si>
+  <si>
+    <t>ED</t>
   </si>
   <si>
     <t>DeviceDefinition.physicalCharacteristics.scoring</t>
@@ -1272,6 +1304,13 @@
     <t>An organization that is responsible for the provision and ongoing maintenance of the device.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
     <t>FiveWs.source</t>
   </si>
   <si>
@@ -1294,6 +1333,10 @@
     <t>used for troubleshooting etc.</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}</t>
+  </si>
+  <si>
     <t>.scopedRole[typeCode=CON].player</t>
   </si>
   <si>
@@ -1337,6 +1380,9 @@
     <t>Descriptive information, usage information or implantation information that is not captured in an existing element.</t>
   </si>
   <si>
+    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
+  </si>
+  <si>
     <t>.text</t>
   </si>
   <si>
@@ -1360,6 +1406,9 @@
   </si>
   <si>
     <t>The parent device it can be part of.</t>
+  </si>
+  <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
   </si>
   <si>
     <t>DeviceDefinition.material</t>
@@ -1749,7 +1798,7 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="35.69140625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="123.23828125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2178,24 +2227,24 @@
         <v>85</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2218,16 +2267,16 @@
         <v>86</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2277,7 +2326,7 @@
         <v>75</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>76</v>
@@ -2286,24 +2335,24 @@
         <v>85</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2326,16 +2375,16 @@
         <v>75</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2361,13 +2410,13 @@
         <v>75</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>75</v>
@@ -2385,7 +2434,7 @@
         <v>75</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>76</v>
@@ -2394,28 +2443,28 @@
         <v>85</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2434,16 +2483,16 @@
         <v>75</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2493,7 +2542,7 @@
         <v>75</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
@@ -2502,28 +2551,28 @@
         <v>85</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2542,16 +2591,16 @@
         <v>75</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2601,7 +2650,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>76</v>
@@ -2619,19 +2668,19 @@
         <v>75</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2650,15 +2699,17 @@
         <v>75</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>135</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>75</v>
@@ -2695,17 +2746,19 @@
         <v>75</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
@@ -2714,27 +2767,27 @@
         <v>77</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>75</v>
@@ -2756,13 +2809,13 @@
         <v>75</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2813,7 +2866,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -2822,10 +2875,10 @@
         <v>77</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>75</v>
@@ -2836,13 +2889,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>75</v>
@@ -2864,13 +2917,13 @@
         <v>75</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2921,7 +2974,7 @@
         <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
@@ -2930,10 +2983,10 @@
         <v>77</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>75</v>
@@ -2944,13 +2997,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>75</v>
@@ -2972,13 +3025,13 @@
         <v>75</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3029,7 +3082,7 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -3038,10 +3091,10 @@
         <v>77</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>75</v>
@@ -3052,14 +3105,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3078,19 +3131,19 @@
         <v>75</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>75</v>
@@ -3127,19 +3180,19 @@
         <v>75</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -3148,24 +3201,24 @@
         <v>77</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3188,13 +3241,13 @@
         <v>75</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3245,7 +3298,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -3254,24 +3307,24 @@
         <v>77</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>75</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3294,13 +3347,13 @@
         <v>75</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3351,7 +3404,7 @@
         <v>75</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -3360,24 +3413,24 @@
         <v>77</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3400,13 +3453,13 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3457,7 +3510,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -3475,19 +3528,19 @@
         <v>75</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>174</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3506,16 +3559,16 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3553,19 +3606,19 @@
         <v>75</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3574,28 +3627,28 @@
         <v>77</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>174</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3614,19 +3667,19 @@
         <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>75</v>
@@ -3675,7 +3728,7 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3684,24 +3737,24 @@
         <v>77</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3724,15 +3777,17 @@
         <v>75</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>75</v>
@@ -3781,7 +3836,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>85</v>
@@ -3790,24 +3845,24 @@
         <v>85</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3830,15 +3885,17 @@
         <v>75</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>75</v>
@@ -3887,7 +3944,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>85</v>
@@ -3896,24 +3953,24 @@
         <v>85</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3936,15 +3993,17 @@
         <v>75</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="M21" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>75</v>
@@ -3993,7 +4052,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>85</v>
@@ -4002,24 +4061,24 @@
         <v>85</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4042,13 +4101,13 @@
         <v>75</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4099,7 +4158,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -4108,24 +4167,24 @@
         <v>85</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4148,13 +4207,13 @@
         <v>75</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4205,7 +4264,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -4214,24 +4273,24 @@
         <v>77</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4254,13 +4313,13 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4311,7 +4370,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -4329,19 +4388,19 @@
         <v>75</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>174</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4360,16 +4419,16 @@
         <v>75</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4407,19 +4466,19 @@
         <v>75</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4428,28 +4487,28 @@
         <v>77</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>174</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4468,19 +4527,19 @@
         <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>75</v>
@@ -4529,7 +4588,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -4538,28 +4597,28 @@
         <v>77</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4578,15 +4637,17 @@
         <v>75</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>75</v>
@@ -4635,7 +4696,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>85</v>
@@ -4644,24 +4705,24 @@
         <v>85</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4684,15 +4745,17 @@
         <v>75</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>75</v>
@@ -4717,31 +4780,31 @@
         <v>75</v>
       </c>
       <c r="X28" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>85</v>
@@ -4750,24 +4813,24 @@
         <v>85</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4790,15 +4853,17 @@
         <v>75</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>75</v>
@@ -4847,7 +4912,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4856,24 +4921,24 @@
         <v>85</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4896,15 +4961,17 @@
         <v>75</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>75</v>
@@ -4929,13 +4996,13 @@
         <v>75</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>75</v>
@@ -4953,7 +5020,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4962,24 +5029,24 @@
         <v>85</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5002,13 +5069,13 @@
         <v>75</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5059,7 +5126,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -5068,24 +5135,24 @@
         <v>77</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5108,13 +5175,13 @@
         <v>75</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5165,7 +5232,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -5183,19 +5250,19 @@
         <v>75</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>174</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5214,16 +5281,16 @@
         <v>75</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5261,19 +5328,19 @@
         <v>75</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -5282,28 +5349,28 @@
         <v>77</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>174</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5322,19 +5389,19 @@
         <v>86</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>75</v>
@@ -5383,7 +5450,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5392,28 +5459,28 @@
         <v>77</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5432,15 +5499,17 @@
         <v>75</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>75</v>
@@ -5489,7 +5558,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>85</v>
@@ -5498,24 +5567,24 @@
         <v>85</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5538,15 +5607,17 @@
         <v>75</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>75</v>
@@ -5595,7 +5666,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5604,24 +5675,24 @@
         <v>85</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5644,15 +5715,17 @@
         <v>75</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>246</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>75</v>
@@ -5701,7 +5774,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5710,24 +5783,24 @@
         <v>77</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5750,15 +5823,17 @@
         <v>86</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>75</v>
@@ -5783,11 +5858,11 @@
         <v>75</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>75</v>
@@ -5805,7 +5880,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5814,24 +5889,24 @@
         <v>77</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5854,13 +5929,13 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5911,7 +5986,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5920,24 +5995,24 @@
         <v>77</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5960,13 +6035,13 @@
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6017,7 +6092,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -6026,24 +6101,24 @@
         <v>85</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6066,13 +6141,13 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6123,7 +6198,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -6141,19 +6216,19 @@
         <v>75</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>174</v>
+        <v>106</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6172,16 +6247,16 @@
         <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6219,19 +6294,19 @@
         <v>75</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>255</v>
+        <v>138</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -6240,27 +6315,27 @@
         <v>77</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>174</v>
+        <v>99</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>75</v>
@@ -6282,13 +6357,13 @@
         <v>75</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6339,7 +6414,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6348,10 +6423,10 @@
         <v>77</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>75</v>
@@ -6362,14 +6437,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6388,19 +6463,19 @@
         <v>86</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>75</v>
@@ -6449,7 +6524,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6458,24 +6533,24 @@
         <v>77</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6498,15 +6573,17 @@
         <v>86</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>75</v>
@@ -6555,7 +6632,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6564,24 +6641,24 @@
         <v>85</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6604,15 +6681,17 @@
         <v>86</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>75</v>
@@ -6661,7 +6740,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6670,24 +6749,24 @@
         <v>85</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6710,15 +6789,17 @@
         <v>86</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>75</v>
@@ -6767,7 +6848,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6776,24 +6857,24 @@
         <v>85</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6816,15 +6897,17 @@
         <v>86</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>75</v>
@@ -6873,7 +6956,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -6882,24 +6965,24 @@
         <v>85</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6922,15 +7005,17 @@
         <v>86</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>75</v>
@@ -6979,7 +7064,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -6988,24 +7073,24 @@
         <v>85</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7028,15 +7113,17 @@
         <v>86</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>75</v>
@@ -7085,7 +7172,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7094,24 +7181,24 @@
         <v>85</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7134,15 +7221,17 @@
         <v>86</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>75</v>
@@ -7191,7 +7280,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7200,24 +7289,24 @@
         <v>85</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7240,15 +7329,17 @@
         <v>86</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>75</v>
@@ -7297,7 +7388,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7306,24 +7397,24 @@
         <v>77</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7346,15 +7437,17 @@
         <v>86</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>75</v>
@@ -7403,7 +7496,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7412,24 +7505,24 @@
         <v>77</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7452,15 +7545,17 @@
         <v>86</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>75</v>
@@ -7509,7 +7604,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7518,24 +7613,24 @@
         <v>77</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>97</v>
+        <v>312</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>75</v>
+        <v>313</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7558,15 +7653,17 @@
         <v>86</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>75</v>
@@ -7615,7 +7712,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -7624,24 +7721,24 @@
         <v>85</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7664,15 +7761,17 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>75</v>
@@ -7721,7 +7820,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -7730,24 +7829,24 @@
         <v>77</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7770,13 +7869,13 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7827,7 +7926,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -7836,24 +7935,24 @@
         <v>77</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7876,13 +7975,13 @@
         <v>75</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7933,7 +8032,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -7951,19 +8050,19 @@
         <v>75</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>174</v>
+        <v>106</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -7982,16 +8081,16 @@
         <v>75</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8029,19 +8128,19 @@
         <v>75</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -8050,28 +8149,28 @@
         <v>77</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>174</v>
+        <v>99</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8090,19 +8189,19 @@
         <v>86</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>75</v>
@@ -8151,7 +8250,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8160,24 +8259,24 @@
         <v>77</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8200,15 +8299,17 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>75</v>
@@ -8257,7 +8358,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>85</v>
@@ -8266,24 +8367,24 @@
         <v>85</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8306,15 +8407,17 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>332</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>75</v>
@@ -8363,7 +8466,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -8372,24 +8475,24 @@
         <v>77</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8412,13 +8515,13 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8457,17 +8560,17 @@
         <v>75</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="AC63" s="2"/>
       <c r="AD63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -8476,24 +8579,24 @@
         <v>77</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8516,13 +8619,13 @@
         <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8573,7 +8676,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -8591,19 +8694,19 @@
         <v>75</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>174</v>
+        <v>106</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8622,16 +8725,16 @@
         <v>75</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8669,19 +8772,19 @@
         <v>75</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -8690,28 +8793,28 @@
         <v>77</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>174</v>
+        <v>99</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -8730,19 +8833,19 @@
         <v>86</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>75</v>
@@ -8791,7 +8894,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -8800,24 +8903,24 @@
         <v>77</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8840,15 +8943,17 @@
         <v>75</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>75</v>
@@ -8897,7 +9002,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>85</v>
@@ -8906,24 +9011,24 @@
         <v>85</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8946,15 +9051,17 @@
         <v>75</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>75</v>
@@ -9003,7 +9110,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -9012,24 +9119,24 @@
         <v>77</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9052,15 +9159,17 @@
         <v>75</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>75</v>
@@ -9109,7 +9218,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9118,27 +9227,27 @@
         <v>77</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="D70" t="s" s="2">
         <v>75</v>
@@ -9160,13 +9269,13 @@
         <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9217,7 +9326,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -9226,24 +9335,24 @@
         <v>77</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9266,13 +9375,13 @@
         <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9323,7 +9432,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -9341,19 +9450,19 @@
         <v>75</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>174</v>
+        <v>106</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -9372,16 +9481,16 @@
         <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9419,19 +9528,19 @@
         <v>75</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -9440,28 +9549,28 @@
         <v>77</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>174</v>
+        <v>99</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -9480,19 +9589,19 @@
         <v>86</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>75</v>
@@ -9541,7 +9650,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -9550,24 +9659,24 @@
         <v>77</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9590,15 +9699,17 @@
         <v>75</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>75</v>
@@ -9608,7 +9719,7 @@
         <v>75</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>75</v>
@@ -9647,7 +9758,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>85</v>
@@ -9656,24 +9767,24 @@
         <v>85</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9696,15 +9807,17 @@
         <v>75</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>75</v>
@@ -9753,7 +9866,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -9762,24 +9875,24 @@
         <v>77</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9802,15 +9915,17 @@
         <v>75</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>75</v>
@@ -9859,7 +9974,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -9868,27 +9983,27 @@
         <v>77</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>75</v>
@@ -9910,13 +10025,13 @@
         <v>75</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -9967,7 +10082,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -9976,24 +10091,24 @@
         <v>77</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10016,13 +10131,13 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10073,7 +10188,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -10091,19 +10206,19 @@
         <v>75</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>174</v>
+        <v>106</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -10122,16 +10237,16 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10169,19 +10284,19 @@
         <v>75</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -10190,28 +10305,28 @@
         <v>77</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>174</v>
+        <v>99</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -10230,19 +10345,19 @@
         <v>86</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>75</v>
@@ -10291,7 +10406,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -10300,24 +10415,24 @@
         <v>77</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10340,15 +10455,17 @@
         <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>75</v>
@@ -10358,7 +10475,7 @@
         <v>75</v>
       </c>
       <c r="S81" t="s" s="2">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="T81" t="s" s="2">
         <v>75</v>
@@ -10397,7 +10514,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>85</v>
@@ -10406,24 +10523,24 @@
         <v>85</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10446,15 +10563,17 @@
         <v>75</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>75</v>
@@ -10503,7 +10622,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -10512,24 +10631,24 @@
         <v>77</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10552,15 +10671,17 @@
         <v>75</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>75</v>
@@ -10609,7 +10730,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -10618,27 +10739,27 @@
         <v>77</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>75</v>
@@ -10660,13 +10781,13 @@
         <v>75</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -10717,7 +10838,7 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -10726,24 +10847,24 @@
         <v>77</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10766,13 +10887,13 @@
         <v>75</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -10823,7 +10944,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -10841,19 +10962,19 @@
         <v>75</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>174</v>
+        <v>106</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -10872,16 +10993,16 @@
         <v>75</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -10919,19 +11040,19 @@
         <v>75</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
@@ -10940,28 +11061,28 @@
         <v>77</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>174</v>
+        <v>99</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -10980,19 +11101,19 @@
         <v>86</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>75</v>
@@ -11041,7 +11162,7 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
@@ -11050,24 +11171,24 @@
         <v>77</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11090,15 +11211,17 @@
         <v>75</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N88" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>75</v>
@@ -11108,7 +11231,7 @@
         <v>75</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>75</v>
@@ -11147,7 +11270,7 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>85</v>
@@ -11156,24 +11279,24 @@
         <v>85</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11196,15 +11319,17 @@
         <v>75</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N89" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>75</v>
@@ -11253,7 +11378,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
@@ -11262,24 +11387,24 @@
         <v>77</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11302,15 +11427,17 @@
         <v>75</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>75</v>
@@ -11359,7 +11486,7 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -11368,27 +11495,27 @@
         <v>77</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="D91" t="s" s="2">
         <v>75</v>
@@ -11410,13 +11537,13 @@
         <v>75</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -11467,7 +11594,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
@@ -11476,24 +11603,24 @@
         <v>77</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11516,13 +11643,13 @@
         <v>75</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -11573,7 +11700,7 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -11591,19 +11718,19 @@
         <v>75</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>174</v>
+        <v>106</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -11622,16 +11749,16 @@
         <v>75</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -11669,19 +11796,19 @@
         <v>75</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -11690,28 +11817,28 @@
         <v>77</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>174</v>
+        <v>99</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -11730,19 +11857,19 @@
         <v>86</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>75</v>
@@ -11791,7 +11918,7 @@
         <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
@@ -11800,24 +11927,24 @@
         <v>77</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11840,15 +11967,17 @@
         <v>75</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>75</v>
@@ -11858,7 +11987,7 @@
         <v>75</v>
       </c>
       <c r="S95" t="s" s="2">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="T95" t="s" s="2">
         <v>75</v>
@@ -11897,7 +12026,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>85</v>
@@ -11906,24 +12035,24 @@
         <v>85</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11946,15 +12075,17 @@
         <v>75</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N96" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>75</v>
@@ -12003,7 +12134,7 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>76</v>
@@ -12012,24 +12143,24 @@
         <v>77</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12052,15 +12183,17 @@
         <v>75</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N97" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>75</v>
@@ -12109,7 +12242,7 @@
         <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>76</v>
@@ -12118,27 +12251,27 @@
         <v>77</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>75</v>
@@ -12160,13 +12293,13 @@
         <v>75</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -12217,7 +12350,7 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>
@@ -12226,24 +12359,24 @@
         <v>77</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12266,13 +12399,13 @@
         <v>75</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -12323,7 +12456,7 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
@@ -12341,19 +12474,19 @@
         <v>75</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>174</v>
+        <v>106</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -12372,16 +12505,16 @@
         <v>75</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -12419,19 +12552,19 @@
         <v>75</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="AC100" t="s" s="2">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="AD100" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>76</v>
@@ -12440,28 +12573,28 @@
         <v>77</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>174</v>
+        <v>99</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -12480,19 +12613,19 @@
         <v>86</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>75</v>
@@ -12541,7 +12674,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>76</v>
@@ -12550,24 +12683,24 @@
         <v>77</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12590,15 +12723,17 @@
         <v>75</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N102" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>75</v>
@@ -12608,7 +12743,7 @@
         <v>75</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="T102" t="s" s="2">
         <v>75</v>
@@ -12647,7 +12782,7 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>85</v>
@@ -12656,24 +12791,24 @@
         <v>85</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12696,15 +12831,17 @@
         <v>75</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>75</v>
@@ -12753,7 +12890,7 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>76</v>
@@ -12762,24 +12899,24 @@
         <v>77</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12802,15 +12939,17 @@
         <v>75</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N104" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>75</v>
@@ -12859,7 +12998,7 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>76</v>
@@ -12868,27 +13007,27 @@
         <v>77</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>75</v>
@@ -12910,13 +13049,13 @@
         <v>75</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -12967,7 +13106,7 @@
         <v>75</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>76</v>
@@ -12976,24 +13115,24 @@
         <v>77</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13016,13 +13155,13 @@
         <v>75</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -13073,7 +13212,7 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>76</v>
@@ -13091,19 +13230,19 @@
         <v>75</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>174</v>
+        <v>106</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -13122,16 +13261,16 @@
         <v>75</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -13169,19 +13308,19 @@
         <v>75</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>76</v>
@@ -13190,28 +13329,28 @@
         <v>77</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>174</v>
+        <v>99</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -13230,19 +13369,19 @@
         <v>86</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>75</v>
@@ -13291,7 +13430,7 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>76</v>
@@ -13300,24 +13439,24 @@
         <v>77</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13340,15 +13479,17 @@
         <v>75</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N109" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>75</v>
@@ -13358,7 +13499,7 @@
         <v>75</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>75</v>
@@ -13397,7 +13538,7 @@
         <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>85</v>
@@ -13406,24 +13547,24 @@
         <v>85</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13446,15 +13587,17 @@
         <v>75</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N110" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>75</v>
@@ -13503,7 +13646,7 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>76</v>
@@ -13512,24 +13655,24 @@
         <v>77</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13552,15 +13695,17 @@
         <v>75</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N111" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>75</v>
@@ -13609,7 +13754,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>76</v>
@@ -13618,24 +13763,24 @@
         <v>77</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13658,15 +13803,17 @@
         <v>75</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N112" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>75</v>
@@ -13715,7 +13862,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>76</v>
@@ -13724,24 +13871,24 @@
         <v>85</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>97</v>
+        <v>408</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>398</v>
+        <v>410</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13764,16 +13911,16 @@
         <v>75</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -13823,7 +13970,7 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>76</v>
@@ -13832,24 +13979,24 @@
         <v>77</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>97</v>
+        <v>416</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>404</v>
+        <v>417</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13872,16 +14019,16 @@
         <v>75</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -13931,7 +14078,7 @@
         <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
@@ -13940,24 +14087,24 @@
         <v>85</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>410</v>
+        <v>423</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13980,15 +14127,17 @@
         <v>75</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N115" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>75</v>
@@ -14037,7 +14186,7 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>76</v>
@@ -14046,24 +14195,24 @@
         <v>85</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14086,15 +14235,17 @@
         <v>75</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N116" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>431</v>
+      </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>75</v>
@@ -14143,7 +14294,7 @@
         <v>75</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>76</v>
@@ -14152,24 +14303,24 @@
         <v>77</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>418</v>
+        <v>432</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14192,15 +14343,17 @@
         <v>75</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N117" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>75</v>
@@ -14249,7 +14402,7 @@
         <v>75</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>76</v>
@@ -14258,24 +14411,24 @@
         <v>85</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14298,15 +14451,17 @@
         <v>86</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N118" s="2"/>
+        <v>439</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>75</v>
@@ -14355,7 +14510,7 @@
         <v>75</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>76</v>
@@ -14364,24 +14519,24 @@
         <v>85</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>97</v>
+        <v>408</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>75</v>
+        <v>440</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14404,13 +14559,13 @@
         <v>75</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -14461,7 +14616,7 @@
         <v>75</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>76</v>
@@ -14470,24 +14625,24 @@
         <v>77</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14510,13 +14665,13 @@
         <v>75</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -14567,7 +14722,7 @@
         <v>75</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>76</v>
@@ -14585,19 +14740,19 @@
         <v>75</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>174</v>
+        <v>106</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
@@ -14616,16 +14771,16 @@
         <v>75</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -14663,19 +14818,19 @@
         <v>75</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>76</v>
@@ -14684,28 +14839,28 @@
         <v>77</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>174</v>
+        <v>99</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>431</v>
+        <v>446</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>431</v>
+        <v>446</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -14724,19 +14879,19 @@
         <v>86</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>75</v>
@@ -14785,7 +14940,7 @@
         <v>75</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>76</v>
@@ -14794,24 +14949,24 @@
         <v>77</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14834,15 +14989,17 @@
         <v>75</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N123" s="2"/>
+        <v>449</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>75</v>
@@ -14891,7 +15048,7 @@
         <v>75</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>85</v>
@@ -14900,24 +15057,24 @@
         <v>85</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14940,13 +15097,13 @@
         <v>75</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -14997,7 +15154,7 @@
         <v>75</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>76</v>
@@ -15006,24 +15163,24 @@
         <v>85</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15046,13 +15203,13 @@
         <v>75</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -15103,7 +15260,7 @@
         <v>75</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>76</v>
@@ -15112,16 +15269,16 @@
         <v>85</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-dmi-devicedefinition.xlsx
+++ b/main/ig/StructureDefinition-dmi-devicedefinition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4277" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4223" uniqueCount="442">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:01:25+00:00</t>
+    <t>2026-03-05T10:22:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -263,7 +263,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Entity. Role, or Act</t>
@@ -310,204 +310,195 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>DeviceDefinition.implicitRules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+  </si>
+  <si>
+    <t>Resource.implicitRules</t>
+  </si>
+  <si>
+    <t>DeviceDefinition.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>A human language.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+  </si>
+  <si>
+    <t>Resource.language</t>
+  </si>
+  <si>
+    <t>DeviceDefinition.text</t>
+  </si>
+  <si>
+    <t>narrative
+htmlxhtmldisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative
+</t>
+  </si>
+  <si>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+  </si>
+  <si>
+    <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t>Act.text?</t>
+  </si>
+  <si>
+    <t>DeviceDefinition.contained</t>
+  </si>
+  <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+  </si>
+  <si>
+    <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>DeviceDefinition.extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>DeviceDefinition.extension:ClasseRisque</t>
+  </si>
+  <si>
+    <t>ClasseRisque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tdmi/StructureDefinition/dmi-classe-risque}
+</t>
+  </si>
+  <si>
+    <t>DMI Classe Risque</t>
+  </si>
+  <si>
+    <t>Extension créée dans ce volet pour représenter la classe de risque.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>DeviceDefinition.extension:ReferenceDistributeur</t>
+  </si>
+  <si>
+    <t>ReferenceDistributeur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tdmi/StructureDefinition/dmi-reference-distributeur}
 </t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>DeviceDefinition.implicitRules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
+    <t>DMI Reference Distributeur</t>
+  </si>
+  <si>
+    <t>Extension créée dans ce volet pour représenter la référence distributeur.</t>
+  </si>
+  <si>
+    <t>DeviceDefinition.extension:CodeEMDN</t>
+  </si>
+  <si>
+    <t>CodeEMDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tdmi/StructureDefinition/dmi-code-emdn}
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
-  </si>
-  <si>
-    <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>DeviceDefinition.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
-  </si>
-  <si>
-    <t>Resource.language</t>
-  </si>
-  <si>
-    <t>DeviceDefinition.text</t>
-  </si>
-  <si>
-    <t>narrative
-htmlxhtmldisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
-  </si>
-  <si>
-    <t>DomainResource.text</t>
-  </si>
-  <si>
-    <t>Act.text?</t>
-  </si>
-  <si>
-    <t>DeviceDefinition.contained</t>
-  </si>
-  <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
-  </si>
-  <si>
-    <t>DomainResource.contained</t>
-  </si>
-  <si>
-    <t>DeviceDefinition.extension</t>
+    <t>DMI Code EMDN</t>
+  </si>
+  <si>
+    <t>Extension créée dans ce volet pour représenter le code EMDN.</t>
+  </si>
+  <si>
+    <t>DeviceDefinition.modifierExtension</t>
   </si>
   <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>DeviceDefinition.extension:ClasseRisque</t>
-  </si>
-  <si>
-    <t>ClasseRisque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tdmi/StructureDefinition/dmi-classe-risque}
-</t>
-  </si>
-  <si>
-    <t>DMI Classe Risque</t>
-  </si>
-  <si>
-    <t>Extension créée dans ce volet pour représenter la classe de risque.</t>
-  </si>
-  <si>
-    <t>DeviceDefinition.extension:ReferenceDistributeur</t>
-  </si>
-  <si>
-    <t>ReferenceDistributeur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tdmi/StructureDefinition/dmi-reference-distributeur}
-</t>
-  </si>
-  <si>
-    <t>DMI Reference Distributeur</t>
-  </si>
-  <si>
-    <t>Extension créée dans ce volet pour représenter la référence distributeur.</t>
-  </si>
-  <si>
-    <t>DeviceDefinition.extension:CodeEMDN</t>
-  </si>
-  <si>
-    <t>CodeEMDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tdmi/StructureDefinition/dmi-code-emdn}
-</t>
-  </si>
-  <si>
-    <t>DMI Code EMDN</t>
-  </si>
-  <si>
-    <t>Extension créée dans ce volet pour représenter le code EMDN.</t>
-  </si>
-  <si>
-    <t>DeviceDefinition.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -515,6 +506,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -537,9 +531,6 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
-    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
-  </si>
-  <si>
     <t>DeviceDefinition.udiDeviceIdentifier</t>
   </si>
   <si>
@@ -569,7 +560,13 @@
     <t>Element.id</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>DeviceDefinition.udiDeviceIdentifier.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -604,9 +601,6 @@
     <t>The identifier that is to be associated with every Device that references this DeviceDefintiion for the issuer and jurisdication porvided in the DeviceDefinition.udiDeviceIdentifier.</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>DeviceDefinition.udiDeviceIdentifier.issuer</t>
   </si>
   <si>
@@ -614,9 +608,6 @@
   </si>
   <si>
     <t>The organization that assigns the identifier algorithm.</t>
-  </si>
-  <si>
-    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
   </si>
   <si>
     <t>DeviceDefinition.udiDeviceIdentifier.jurisdiction</t>
@@ -725,9 +716,6 @@
     <t>What kind of device or device system this is.</t>
   </si>
   <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
     <t>example</t>
   </si>
   <si>
@@ -735,9 +723,6 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/device-kind|4.0.1</t>
-  </si>
-  <si>
-    <t>CD</t>
   </si>
   <si>
     <t>DeviceDefinition.specialization</t>
@@ -826,6 +811,9 @@
     <t>DeviceDefinition.physicalCharacteristics.extension</t>
   </si>
   <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
     <t>DeviceDefinition.physicalCharacteristics.extension:InternalDiameter</t>
   </si>
   <si>
@@ -858,17 +846,7 @@
     <t>Where applicable, the height can be specified using a numerical value and its unit of measurement The unit of measurement shall be specified in accordance with ISO 11240 and the resulting terminology The symbol and the symbol identifier shall be used.</t>
   </si>
   <si>
-    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
-  </si>
-  <si>
     <t>ProdCharacteristic.height</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
   </si>
   <si>
     <t>DeviceDefinition.physicalCharacteristics.width</t>
@@ -980,17 +958,7 @@
     <t>Where applicable, the image can be provided The format of the image attachment shall be specified by regional implementations.</t>
   </si>
   <si>
-    <t>When providing a summary view (for example with Observation.value[x]) Attachment should be represented with a brief display text such as "Signed Procedure Consent".</t>
-  </si>
-  <si>
     <t>ProdCharacteristic.image</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-att-1:If the Attachment has data, it SHALL have a contentType {data.empty() or contentType.exists()}</t>
-  </si>
-  <si>
-    <t>ED</t>
   </si>
   <si>
     <t>DeviceDefinition.physicalCharacteristics.scoring</t>
@@ -1304,13 +1272,6 @@
     <t>An organization that is responsible for the provision and ongoing maintenance of the device.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
     <t>FiveWs.source</t>
   </si>
   <si>
@@ -1333,10 +1294,6 @@
     <t>used for troubleshooting etc.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}</t>
-  </si>
-  <si>
     <t>.scopedRole[typeCode=CON].player</t>
   </si>
   <si>
@@ -1380,9 +1337,6 @@
     <t>Descriptive information, usage information or implantation information that is not captured in an existing element.</t>
   </si>
   <si>
-    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
-  </si>
-  <si>
     <t>.text</t>
   </si>
   <si>
@@ -1406,9 +1360,6 @@
   </si>
   <si>
     <t>The parent device it can be part of.</t>
-  </si>
-  <si>
-    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
   </si>
   <si>
     <t>DeviceDefinition.material</t>
@@ -1798,7 +1749,7 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="123.23828125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="35.69140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2227,24 +2178,24 @@
         <v>85</v>
       </c>
       <c r="AI4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ4" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK4" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2267,16 +2218,16 @@
         <v>86</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L5" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>104</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2326,7 +2277,7 @@
         <v>75</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>76</v>
@@ -2335,24 +2286,24 @@
         <v>85</v>
       </c>
       <c r="AI5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ5" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ5" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK5" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2375,16 +2326,16 @@
         <v>75</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M6" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N6" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="L6" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2410,31 +2361,31 @@
         <v>75</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="Y6" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Z6" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>76</v>
@@ -2443,28 +2394,28 @@
         <v>85</v>
       </c>
       <c r="AI6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ6" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2483,16 +2434,16 @@
         <v>75</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="N7" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2542,7 +2493,7 @@
         <v>75</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
@@ -2551,28 +2502,28 @@
         <v>85</v>
       </c>
       <c r="AI7" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ7" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2591,16 +2542,16 @@
         <v>75</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="N8" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="L8" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2650,7 +2601,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>76</v>
@@ -2668,19 +2619,19 @@
         <v>75</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>99</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2699,17 +2650,15 @@
         <v>75</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>75</v>
@@ -2746,19 +2695,17 @@
         <v>75</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
@@ -2767,27 +2714,27 @@
         <v>77</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>75</v>
@@ -2809,13 +2756,13 @@
         <v>75</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2866,7 +2813,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -2875,10 +2822,10 @@
         <v>77</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>97</v>
+        <v>142</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>75</v>
@@ -2889,13 +2836,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>75</v>
@@ -2917,13 +2864,13 @@
         <v>75</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2974,7 +2921,7 @@
         <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
@@ -2983,10 +2930,10 @@
         <v>77</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>97</v>
+        <v>142</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>75</v>
@@ -2997,13 +2944,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>75</v>
@@ -3025,13 +2972,13 @@
         <v>75</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3082,7 +3029,7 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -3091,10 +3038,10 @@
         <v>77</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>97</v>
+        <v>142</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>75</v>
@@ -3105,14 +3052,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3131,19 +3078,19 @@
         <v>75</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O13" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>75</v>
@@ -3180,19 +3127,19 @@
         <v>75</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -3201,24 +3148,24 @@
         <v>77</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>99</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3241,13 +3188,13 @@
         <v>75</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3298,7 +3245,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -3307,24 +3254,24 @@
         <v>77</v>
       </c>
       <c r="AI14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ14" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK14" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>167</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3347,13 +3294,13 @@
         <v>75</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3404,7 +3351,7 @@
         <v>75</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -3413,24 +3360,24 @@
         <v>77</v>
       </c>
       <c r="AI15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ15" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3453,13 +3400,13 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3510,7 +3457,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -3528,19 +3475,19 @@
         <v>75</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>106</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3559,16 +3506,16 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3606,19 +3553,19 @@
         <v>75</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3627,28 +3574,28 @@
         <v>77</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>99</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3667,19 +3614,19 @@
         <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M18" t="s" s="2">
-        <v>183</v>
-      </c>
       <c r="N18" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>75</v>
@@ -3728,7 +3675,7 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3737,24 +3684,24 @@
         <v>77</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>99</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3777,17 +3724,15 @@
         <v>75</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="M19" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>188</v>
-      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>75</v>
@@ -3836,7 +3781,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>85</v>
@@ -3845,24 +3790,24 @@
         <v>85</v>
       </c>
       <c r="AI19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ19" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3885,17 +3830,15 @@
         <v>75</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>75</v>
@@ -3944,7 +3887,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>85</v>
@@ -3953,24 +3896,24 @@
         <v>85</v>
       </c>
       <c r="AI20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ20" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3993,17 +3936,15 @@
         <v>75</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N21" t="s" s="2">
         <v>192</v>
       </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>75</v>
@@ -4052,7 +3993,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>85</v>
@@ -4061,24 +4002,24 @@
         <v>85</v>
       </c>
       <c r="AI21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ21" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4101,13 +4042,13 @@
         <v>75</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4158,7 +4099,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -4167,24 +4108,24 @@
         <v>85</v>
       </c>
       <c r="AI22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ22" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK22" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4207,13 +4148,13 @@
         <v>75</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4264,7 +4205,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -4273,24 +4214,24 @@
         <v>77</v>
       </c>
       <c r="AI23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ23" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4313,13 +4254,13 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4370,7 +4311,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -4388,19 +4329,19 @@
         <v>75</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>106</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4419,16 +4360,16 @@
         <v>75</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4466,19 +4407,19 @@
         <v>75</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4487,28 +4428,28 @@
         <v>77</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>99</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4527,19 +4468,19 @@
         <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M26" t="s" s="2">
-        <v>183</v>
-      </c>
       <c r="N26" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>75</v>
@@ -4588,7 +4529,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -4597,28 +4538,28 @@
         <v>77</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>99</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4637,17 +4578,15 @@
         <v>75</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>75</v>
@@ -4696,7 +4635,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>85</v>
@@ -4705,24 +4644,24 @@
         <v>85</v>
       </c>
       <c r="AI27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ27" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4745,17 +4684,15 @@
         <v>75</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>75</v>
@@ -4780,13 +4717,13 @@
         <v>75</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>75</v>
@@ -4804,7 +4741,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>85</v>
@@ -4813,24 +4750,24 @@
         <v>85</v>
       </c>
       <c r="AI28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ28" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK28" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4853,17 +4790,15 @@
         <v>75</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>75</v>
@@ -4912,7 +4847,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4921,24 +4856,24 @@
         <v>85</v>
       </c>
       <c r="AI29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ29" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK29" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4961,17 +4896,15 @@
         <v>75</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>75</v>
@@ -4996,13 +4929,13 @@
         <v>75</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>75</v>
@@ -5020,7 +4953,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -5029,24 +4962,24 @@
         <v>85</v>
       </c>
       <c r="AI30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ30" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>231</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5069,13 +5002,13 @@
         <v>75</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5126,7 +5059,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -5135,24 +5068,24 @@
         <v>77</v>
       </c>
       <c r="AI31" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ31" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5175,13 +5108,13 @@
         <v>75</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5232,7 +5165,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -5250,19 +5183,19 @@
         <v>75</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>106</v>
+        <v>174</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5281,16 +5214,16 @@
         <v>75</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5328,19 +5261,19 @@
         <v>75</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -5349,28 +5282,28 @@
         <v>77</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>99</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5389,19 +5322,19 @@
         <v>86</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M34" t="s" s="2">
-        <v>183</v>
-      </c>
       <c r="N34" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>75</v>
@@ -5450,7 +5383,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5459,28 +5392,28 @@
         <v>77</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>99</v>
+        <v>128</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5499,17 +5432,15 @@
         <v>75</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>75</v>
@@ -5558,7 +5489,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>85</v>
@@ -5567,24 +5498,24 @@
         <v>85</v>
       </c>
       <c r="AI35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ35" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5607,17 +5538,15 @@
         <v>75</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>75</v>
@@ -5666,7 +5595,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5675,24 +5604,24 @@
         <v>85</v>
       </c>
       <c r="AI36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ36" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK36" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5715,17 +5644,15 @@
         <v>75</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>75</v>
@@ -5774,7 +5701,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5783,24 +5710,24 @@
         <v>77</v>
       </c>
       <c r="AI37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ37" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5823,17 +5750,15 @@
         <v>86</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>75</v>
@@ -5858,11 +5783,11 @@
         <v>75</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>75</v>
@@ -5880,7 +5805,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5889,24 +5814,24 @@
         <v>77</v>
       </c>
       <c r="AI38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ38" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>231</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5929,13 +5854,13 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5986,7 +5911,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5995,24 +5920,24 @@
         <v>77</v>
       </c>
       <c r="AI39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ39" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6035,13 +5960,13 @@
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6092,7 +6017,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -6101,24 +6026,24 @@
         <v>85</v>
       </c>
       <c r="AI40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ40" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6141,13 +6066,13 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6198,7 +6123,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -6216,19 +6141,19 @@
         <v>75</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>106</v>
+        <v>174</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6247,16 +6172,16 @@
         <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6294,19 +6219,19 @@
         <v>75</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>138</v>
+        <v>255</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -6315,27 +6240,27 @@
         <v>77</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>99</v>
+        <v>174</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>75</v>
@@ -6357,13 +6282,13 @@
         <v>75</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6414,7 +6339,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6423,10 +6348,10 @@
         <v>77</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>75</v>
@@ -6437,14 +6362,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6463,19 +6388,19 @@
         <v>86</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M44" t="s" s="2">
-        <v>183</v>
-      </c>
       <c r="N44" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>75</v>
@@ -6524,7 +6449,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6533,24 +6458,24 @@
         <v>77</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>99</v>
+        <v>128</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6573,17 +6498,15 @@
         <v>86</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>75</v>
@@ -6632,7 +6555,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6641,24 +6564,24 @@
         <v>85</v>
       </c>
       <c r="AI45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ45" t="s" s="2">
-        <v>272</v>
-      </c>
       <c r="AK45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>273</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6681,17 +6604,15 @@
         <v>86</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>75</v>
@@ -6740,7 +6661,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6749,24 +6670,24 @@
         <v>85</v>
       </c>
       <c r="AI46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ46" t="s" s="2">
-        <v>272</v>
-      </c>
       <c r="AK46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>273</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6789,17 +6710,15 @@
         <v>86</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>75</v>
@@ -6848,7 +6767,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6857,24 +6776,24 @@
         <v>85</v>
       </c>
       <c r="AI47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ47" t="s" s="2">
-        <v>272</v>
-      </c>
       <c r="AK47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>273</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6897,17 +6816,15 @@
         <v>86</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>75</v>
@@ -6956,7 +6873,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -6965,24 +6882,24 @@
         <v>85</v>
       </c>
       <c r="AI48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ48" t="s" s="2">
-        <v>272</v>
-      </c>
       <c r="AK48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>273</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7005,17 +6922,15 @@
         <v>86</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>75</v>
@@ -7064,7 +6979,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -7073,24 +6988,24 @@
         <v>85</v>
       </c>
       <c r="AI49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ49" t="s" s="2">
-        <v>272</v>
-      </c>
       <c r="AK49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>273</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7113,17 +7028,15 @@
         <v>86</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>75</v>
@@ -7172,7 +7085,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7181,24 +7094,24 @@
         <v>85</v>
       </c>
       <c r="AI50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ50" t="s" s="2">
-        <v>272</v>
-      </c>
       <c r="AK50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>273</v>
+        <v>75</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7221,17 +7134,15 @@
         <v>86</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>75</v>
@@ -7280,7 +7191,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7289,24 +7200,24 @@
         <v>85</v>
       </c>
       <c r="AI51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ51" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7329,17 +7240,15 @@
         <v>86</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>75</v>
@@ -7388,7 +7297,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7397,24 +7306,24 @@
         <v>77</v>
       </c>
       <c r="AI52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ52" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7437,17 +7346,15 @@
         <v>86</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>75</v>
@@ -7496,7 +7403,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7505,24 +7412,24 @@
         <v>77</v>
       </c>
       <c r="AI53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ53" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7545,17 +7452,15 @@
         <v>86</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>75</v>
@@ -7604,7 +7509,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7613,24 +7518,24 @@
         <v>77</v>
       </c>
       <c r="AI54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ54" t="s" s="2">
-        <v>312</v>
-      </c>
       <c r="AK54" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>313</v>
+        <v>75</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7653,17 +7558,15 @@
         <v>86</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>75</v>
@@ -7712,7 +7615,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -7721,24 +7624,24 @@
         <v>85</v>
       </c>
       <c r="AI55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ55" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>231</v>
+        <v>75</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7761,17 +7664,15 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>75</v>
@@ -7820,7 +7721,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -7829,24 +7730,24 @@
         <v>77</v>
       </c>
       <c r="AI56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ56" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>231</v>
+        <v>75</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7869,13 +7770,13 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7926,7 +7827,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -7935,24 +7836,24 @@
         <v>77</v>
       </c>
       <c r="AI57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ57" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7975,13 +7876,13 @@
         <v>75</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8032,7 +7933,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -8050,19 +7951,19 @@
         <v>75</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>106</v>
+        <v>174</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8081,16 +7982,16 @@
         <v>75</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8128,19 +8029,19 @@
         <v>75</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -8149,28 +8050,28 @@
         <v>77</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>99</v>
+        <v>174</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8189,19 +8090,19 @@
         <v>86</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M60" t="s" s="2">
-        <v>183</v>
-      </c>
       <c r="N60" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>75</v>
@@ -8250,7 +8151,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8259,24 +8160,24 @@
         <v>77</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>99</v>
+        <v>128</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8299,17 +8200,15 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>75</v>
@@ -8358,7 +8257,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>85</v>
@@ -8367,24 +8266,24 @@
         <v>85</v>
       </c>
       <c r="AI61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ61" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK61" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>231</v>
+        <v>75</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8407,17 +8306,15 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>75</v>
@@ -8466,7 +8363,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -8475,24 +8372,24 @@
         <v>77</v>
       </c>
       <c r="AI62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ62" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>231</v>
+        <v>75</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8515,13 +8412,13 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8560,17 +8457,17 @@
         <v>75</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="AC63" s="2"/>
       <c r="AD63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -8579,24 +8476,24 @@
         <v>77</v>
       </c>
       <c r="AI63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ63" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8619,13 +8516,13 @@
         <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8676,7 +8573,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -8694,19 +8591,19 @@
         <v>75</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>106</v>
+        <v>174</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8725,16 +8622,16 @@
         <v>75</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8772,19 +8669,19 @@
         <v>75</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -8793,28 +8690,28 @@
         <v>77</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>99</v>
+        <v>174</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -8833,19 +8730,19 @@
         <v>86</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M66" t="s" s="2">
-        <v>183</v>
-      </c>
       <c r="N66" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>75</v>
@@ -8894,7 +8791,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -8903,24 +8800,24 @@
         <v>77</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>99</v>
+        <v>128</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8943,17 +8840,15 @@
         <v>75</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>75</v>
@@ -9002,7 +8897,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>85</v>
@@ -9011,24 +8906,24 @@
         <v>85</v>
       </c>
       <c r="AI67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ67" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>231</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9051,17 +8946,15 @@
         <v>75</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>75</v>
@@ -9110,7 +9003,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -9119,24 +9012,24 @@
         <v>77</v>
       </c>
       <c r="AI68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ68" t="s" s="2">
-        <v>272</v>
-      </c>
       <c r="AK68" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>273</v>
+        <v>75</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9159,17 +9052,15 @@
         <v>75</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>75</v>
@@ -9218,7 +9109,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9227,27 +9118,27 @@
         <v>77</v>
       </c>
       <c r="AI69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ69" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK69" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>231</v>
+        <v>75</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="D70" t="s" s="2">
         <v>75</v>
@@ -9269,13 +9160,13 @@
         <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9326,7 +9217,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -9335,24 +9226,24 @@
         <v>77</v>
       </c>
       <c r="AI70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ70" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK70" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9375,13 +9266,13 @@
         <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9432,7 +9323,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -9450,19 +9341,19 @@
         <v>75</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>106</v>
+        <v>174</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -9481,16 +9372,16 @@
         <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9528,19 +9419,19 @@
         <v>75</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -9549,28 +9440,28 @@
         <v>77</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>99</v>
+        <v>174</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -9589,19 +9480,19 @@
         <v>86</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M73" t="s" s="2">
-        <v>183</v>
-      </c>
       <c r="N73" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>75</v>
@@ -9650,7 +9541,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -9659,24 +9550,24 @@
         <v>77</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>99</v>
+        <v>128</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9699,17 +9590,15 @@
         <v>75</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>75</v>
@@ -9719,7 +9608,7 @@
         <v>75</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>75</v>
@@ -9758,7 +9647,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>85</v>
@@ -9767,24 +9656,24 @@
         <v>85</v>
       </c>
       <c r="AI74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ74" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK74" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>231</v>
+        <v>75</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9807,17 +9696,15 @@
         <v>75</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>75</v>
@@ -9866,7 +9753,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -9875,24 +9762,24 @@
         <v>77</v>
       </c>
       <c r="AI75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ75" t="s" s="2">
-        <v>272</v>
-      </c>
       <c r="AK75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>273</v>
+        <v>75</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9915,17 +9802,15 @@
         <v>75</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>75</v>
@@ -9974,7 +9859,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -9983,27 +9868,27 @@
         <v>77</v>
       </c>
       <c r="AI76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ76" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK76" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>231</v>
+        <v>75</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>75</v>
@@ -10025,13 +9910,13 @@
         <v>75</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10082,7 +9967,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -10091,24 +9976,24 @@
         <v>77</v>
       </c>
       <c r="AI77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ77" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK77" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10131,13 +10016,13 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10188,7 +10073,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -10206,19 +10091,19 @@
         <v>75</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>106</v>
+        <v>174</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -10237,16 +10122,16 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10284,19 +10169,19 @@
         <v>75</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -10305,28 +10190,28 @@
         <v>77</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>99</v>
+        <v>174</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -10345,19 +10230,19 @@
         <v>86</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M80" t="s" s="2">
-        <v>183</v>
-      </c>
       <c r="N80" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>75</v>
@@ -10406,7 +10291,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -10415,24 +10300,24 @@
         <v>77</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>99</v>
+        <v>128</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10455,17 +10340,15 @@
         <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>75</v>
@@ -10475,7 +10358,7 @@
         <v>75</v>
       </c>
       <c r="S81" t="s" s="2">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="T81" t="s" s="2">
         <v>75</v>
@@ -10514,7 +10397,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>85</v>
@@ -10523,24 +10406,24 @@
         <v>85</v>
       </c>
       <c r="AI81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ81" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK81" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>231</v>
+        <v>75</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10563,17 +10446,15 @@
         <v>75</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>75</v>
@@ -10622,7 +10503,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -10631,24 +10512,24 @@
         <v>77</v>
       </c>
       <c r="AI82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ82" t="s" s="2">
-        <v>272</v>
-      </c>
       <c r="AK82" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>273</v>
+        <v>75</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10671,17 +10552,15 @@
         <v>75</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>75</v>
@@ -10730,7 +10609,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -10739,27 +10618,27 @@
         <v>77</v>
       </c>
       <c r="AI83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ83" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK83" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>231</v>
+        <v>75</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>75</v>
@@ -10781,13 +10660,13 @@
         <v>75</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -10838,7 +10717,7 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -10847,24 +10726,24 @@
         <v>77</v>
       </c>
       <c r="AI84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ84" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK84" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10887,13 +10766,13 @@
         <v>75</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -10944,7 +10823,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -10962,19 +10841,19 @@
         <v>75</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>106</v>
+        <v>174</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -10993,16 +10872,16 @@
         <v>75</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11040,19 +10919,19 @@
         <v>75</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
@@ -11061,28 +10940,28 @@
         <v>77</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>99</v>
+        <v>174</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -11101,19 +10980,19 @@
         <v>86</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M87" t="s" s="2">
-        <v>183</v>
-      </c>
       <c r="N87" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>75</v>
@@ -11162,7 +11041,7 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
@@ -11171,24 +11050,24 @@
         <v>77</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>99</v>
+        <v>128</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11211,17 +11090,15 @@
         <v>75</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>75</v>
@@ -11231,7 +11108,7 @@
         <v>75</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>75</v>
@@ -11270,7 +11147,7 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>85</v>
@@ -11279,24 +11156,24 @@
         <v>85</v>
       </c>
       <c r="AI88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ88" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK88" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>231</v>
+        <v>75</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11319,17 +11196,15 @@
         <v>75</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>75</v>
@@ -11378,7 +11253,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
@@ -11387,24 +11262,24 @@
         <v>77</v>
       </c>
       <c r="AI89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ89" t="s" s="2">
-        <v>272</v>
-      </c>
       <c r="AK89" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>273</v>
+        <v>75</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11427,17 +11302,15 @@
         <v>75</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>75</v>
@@ -11486,7 +11359,7 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -11495,27 +11368,27 @@
         <v>77</v>
       </c>
       <c r="AI90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ90" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK90" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>231</v>
+        <v>75</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="D91" t="s" s="2">
         <v>75</v>
@@ -11537,13 +11410,13 @@
         <v>75</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -11594,7 +11467,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
@@ -11603,24 +11476,24 @@
         <v>77</v>
       </c>
       <c r="AI91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ91" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK91" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11643,13 +11516,13 @@
         <v>75</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -11700,7 +11573,7 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -11718,19 +11591,19 @@
         <v>75</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>106</v>
+        <v>174</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -11749,16 +11622,16 @@
         <v>75</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -11796,19 +11669,19 @@
         <v>75</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -11817,28 +11690,28 @@
         <v>77</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>99</v>
+        <v>174</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -11857,19 +11730,19 @@
         <v>86</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M94" t="s" s="2">
-        <v>183</v>
-      </c>
       <c r="N94" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>75</v>
@@ -11918,7 +11791,7 @@
         <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
@@ -11927,24 +11800,24 @@
         <v>77</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>99</v>
+        <v>128</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11967,17 +11840,15 @@
         <v>75</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>75</v>
@@ -11987,7 +11858,7 @@
         <v>75</v>
       </c>
       <c r="S95" t="s" s="2">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="T95" t="s" s="2">
         <v>75</v>
@@ -12026,7 +11897,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>85</v>
@@ -12035,24 +11906,24 @@
         <v>85</v>
       </c>
       <c r="AI95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ95" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK95" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>231</v>
+        <v>75</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12075,17 +11946,15 @@
         <v>75</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>75</v>
@@ -12134,7 +12003,7 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>76</v>
@@ -12143,24 +12012,24 @@
         <v>77</v>
       </c>
       <c r="AI96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ96" t="s" s="2">
-        <v>272</v>
-      </c>
       <c r="AK96" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>273</v>
+        <v>75</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12183,17 +12052,15 @@
         <v>75</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>75</v>
@@ -12242,7 +12109,7 @@
         <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>76</v>
@@ -12251,27 +12118,27 @@
         <v>77</v>
       </c>
       <c r="AI97" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ97" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK97" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>231</v>
+        <v>75</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>75</v>
@@ -12293,13 +12160,13 @@
         <v>75</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -12350,7 +12217,7 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>
@@ -12359,24 +12226,24 @@
         <v>77</v>
       </c>
       <c r="AI98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ98" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK98" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12399,13 +12266,13 @@
         <v>75</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -12456,7 +12323,7 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
@@ -12474,19 +12341,19 @@
         <v>75</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>106</v>
+        <v>174</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -12505,16 +12372,16 @@
         <v>75</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -12552,19 +12419,19 @@
         <v>75</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="AC100" t="s" s="2">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="AD100" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>76</v>
@@ -12573,28 +12440,28 @@
         <v>77</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>99</v>
+        <v>174</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -12613,19 +12480,19 @@
         <v>86</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M101" t="s" s="2">
-        <v>183</v>
-      </c>
       <c r="N101" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>75</v>
@@ -12674,7 +12541,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>76</v>
@@ -12683,24 +12550,24 @@
         <v>77</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>99</v>
+        <v>128</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12723,17 +12590,15 @@
         <v>75</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>75</v>
@@ -12743,7 +12608,7 @@
         <v>75</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="T102" t="s" s="2">
         <v>75</v>
@@ -12782,7 +12647,7 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>85</v>
@@ -12791,24 +12656,24 @@
         <v>85</v>
       </c>
       <c r="AI102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ102" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK102" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>231</v>
+        <v>75</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12831,17 +12696,15 @@
         <v>75</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>75</v>
@@ -12890,7 +12753,7 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>76</v>
@@ -12899,24 +12762,24 @@
         <v>77</v>
       </c>
       <c r="AI103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ103" t="s" s="2">
-        <v>272</v>
-      </c>
       <c r="AK103" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>273</v>
+        <v>75</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12939,17 +12802,15 @@
         <v>75</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>75</v>
@@ -12998,7 +12859,7 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>76</v>
@@ -13007,27 +12868,27 @@
         <v>77</v>
       </c>
       <c r="AI104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ104" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK104" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>231</v>
+        <v>75</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>75</v>
@@ -13049,13 +12910,13 @@
         <v>75</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -13106,7 +12967,7 @@
         <v>75</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>76</v>
@@ -13115,24 +12976,24 @@
         <v>77</v>
       </c>
       <c r="AI105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ105" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK105" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13155,13 +13016,13 @@
         <v>75</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -13212,7 +13073,7 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>76</v>
@@ -13230,19 +13091,19 @@
         <v>75</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>106</v>
+        <v>174</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -13261,16 +13122,16 @@
         <v>75</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -13308,19 +13169,19 @@
         <v>75</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>76</v>
@@ -13329,28 +13190,28 @@
         <v>77</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>99</v>
+        <v>174</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -13369,19 +13230,19 @@
         <v>86</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M108" t="s" s="2">
-        <v>183</v>
-      </c>
       <c r="N108" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>75</v>
@@ -13430,7 +13291,7 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>76</v>
@@ -13439,24 +13300,24 @@
         <v>77</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>99</v>
+        <v>128</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13479,17 +13340,15 @@
         <v>75</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>75</v>
@@ -13499,7 +13358,7 @@
         <v>75</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>75</v>
@@ -13538,7 +13397,7 @@
         <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>85</v>
@@ -13547,24 +13406,24 @@
         <v>85</v>
       </c>
       <c r="AI109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ109" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK109" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>231</v>
+        <v>75</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13587,17 +13446,15 @@
         <v>75</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="N110" s="2"/>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>75</v>
@@ -13646,7 +13503,7 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>76</v>
@@ -13655,24 +13512,24 @@
         <v>77</v>
       </c>
       <c r="AI110" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ110" t="s" s="2">
-        <v>272</v>
-      </c>
       <c r="AK110" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>273</v>
+        <v>75</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13695,17 +13552,15 @@
         <v>75</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>75</v>
@@ -13754,7 +13609,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>76</v>
@@ -13763,24 +13618,24 @@
         <v>77</v>
       </c>
       <c r="AI111" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ111" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK111" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>231</v>
+        <v>75</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13803,17 +13658,15 @@
         <v>75</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>407</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>75</v>
@@ -13862,7 +13715,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>76</v>
@@ -13871,24 +13724,24 @@
         <v>85</v>
       </c>
       <c r="AI112" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ112" t="s" s="2">
-        <v>408</v>
-      </c>
       <c r="AK112" t="s" s="2">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>410</v>
+        <v>398</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13911,16 +13764,16 @@
         <v>75</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -13970,7 +13823,7 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>76</v>
@@ -13979,24 +13832,24 @@
         <v>77</v>
       </c>
       <c r="AI113" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ113" t="s" s="2">
-        <v>416</v>
-      </c>
       <c r="AK113" t="s" s="2">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>417</v>
+        <v>404</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>418</v>
+        <v>405</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>418</v>
+        <v>405</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14019,16 +13872,16 @@
         <v>75</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -14078,7 +13931,7 @@
         <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>418</v>
+        <v>405</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
@@ -14087,24 +13940,24 @@
         <v>85</v>
       </c>
       <c r="AI114" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ114" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK114" t="s" s="2">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>423</v>
+        <v>410</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14127,17 +13980,15 @@
         <v>75</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="N115" s="2"/>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>75</v>
@@ -14186,7 +14037,7 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>76</v>
@@ -14195,24 +14046,24 @@
         <v>85</v>
       </c>
       <c r="AI115" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ115" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK115" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14235,17 +14086,15 @@
         <v>75</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>431</v>
-      </c>
+        <v>417</v>
+      </c>
+      <c r="N116" s="2"/>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>75</v>
@@ -14294,7 +14143,7 @@
         <v>75</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>76</v>
@@ -14303,24 +14152,24 @@
         <v>77</v>
       </c>
       <c r="AI116" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ116" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK116" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>432</v>
+        <v>418</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14343,17 +14192,15 @@
         <v>75</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>434</v>
+        <v>420</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="N117" s="2"/>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>75</v>
@@ -14402,7 +14249,7 @@
         <v>75</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>76</v>
@@ -14411,24 +14258,24 @@
         <v>85</v>
       </c>
       <c r="AI117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ117" t="s" s="2">
-        <v>272</v>
-      </c>
       <c r="AK117" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>273</v>
+        <v>75</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14451,17 +14298,15 @@
         <v>86</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>438</v>
+        <v>424</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>407</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>75</v>
@@ -14510,7 +14355,7 @@
         <v>75</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>76</v>
@@ -14519,24 +14364,24 @@
         <v>85</v>
       </c>
       <c r="AI118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ118" t="s" s="2">
-        <v>408</v>
-      </c>
       <c r="AK118" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>440</v>
+        <v>75</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14559,13 +14404,13 @@
         <v>75</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -14616,7 +14461,7 @@
         <v>75</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>76</v>
@@ -14625,24 +14470,24 @@
         <v>77</v>
       </c>
       <c r="AI119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ119" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK119" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14665,13 +14510,13 @@
         <v>75</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -14722,7 +14567,7 @@
         <v>75</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>76</v>
@@ -14740,19 +14585,19 @@
         <v>75</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>106</v>
+        <v>174</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
@@ -14771,16 +14616,16 @@
         <v>75</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -14818,19 +14663,19 @@
         <v>75</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>76</v>
@@ -14839,28 +14684,28 @@
         <v>77</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>99</v>
+        <v>174</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>446</v>
+        <v>431</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>446</v>
+        <v>431</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -14879,19 +14724,19 @@
         <v>86</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M122" t="s" s="2">
-        <v>183</v>
-      </c>
       <c r="N122" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>75</v>
@@ -14940,7 +14785,7 @@
         <v>75</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>76</v>
@@ -14949,24 +14794,24 @@
         <v>77</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>99</v>
+        <v>128</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14989,17 +14834,15 @@
         <v>75</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="N123" s="2"/>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>75</v>
@@ -15048,7 +14891,7 @@
         <v>75</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>85</v>
@@ -15057,24 +14900,24 @@
         <v>85</v>
       </c>
       <c r="AI123" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ123" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK123" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>231</v>
+        <v>75</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15097,13 +14940,13 @@
         <v>75</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -15154,7 +14997,7 @@
         <v>75</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>76</v>
@@ -15163,24 +15006,24 @@
         <v>85</v>
       </c>
       <c r="AI124" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ124" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK124" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15203,13 +15046,13 @@
         <v>75</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -15260,7 +15103,7 @@
         <v>75</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>76</v>
@@ -15269,16 +15112,16 @@
         <v>85</v>
       </c>
       <c r="AI125" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AJ125" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AK125" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-dmi-devicedefinition.xlsx
+++ b/main/ig/StructureDefinition-dmi-devicedefinition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:22:34+00:00</t>
+    <t>2026-03-05T10:23:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-devicedefinition.xlsx
+++ b/main/ig/StructureDefinition-dmi-devicedefinition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4223" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4277" uniqueCount="457">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:23:55+00:00</t>
+    <t>2026-03-05T10:25:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -263,7 +263,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
   </si>
   <si>
     <t>Entity. Role, or Act</t>
@@ -310,10 +310,17 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>DeviceDefinition.implicitRules</t>
   </si>
   <si>
@@ -333,6 +340,9 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>DeviceDefinition.language</t>
   </si>
   <si>
@@ -410,26 +420,33 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>DeviceDefinition.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
   </si>
   <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
 </t>
   </si>
   <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
     <t>open</t>
   </si>
   <si>
@@ -456,10 +473,6 @@
     <t>Extension créée dans ce volet pour représenter la classe de risque.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>DeviceDefinition.extension:ReferenceDistributeur</t>
   </si>
   <si>
@@ -495,10 +508,6 @@
     <t>DeviceDefinition.modifierExtension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -506,9 +515,6 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -531,6 +537,9 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
+    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
+  </si>
+  <si>
     <t>DeviceDefinition.udiDeviceIdentifier</t>
   </si>
   <si>
@@ -560,13 +569,7 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>DeviceDefinition.udiDeviceIdentifier.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -601,6 +604,9 @@
     <t>The identifier that is to be associated with every Device that references this DeviceDefintiion for the issuer and jurisdication porvided in the DeviceDefinition.udiDeviceIdentifier.</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>DeviceDefinition.udiDeviceIdentifier.issuer</t>
   </si>
   <si>
@@ -608,6 +614,9 @@
   </si>
   <si>
     <t>The organization that assigns the identifier algorithm.</t>
+  </si>
+  <si>
+    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
   </si>
   <si>
     <t>DeviceDefinition.udiDeviceIdentifier.jurisdiction</t>
@@ -716,6 +725,9 @@
     <t>What kind of device or device system this is.</t>
   </si>
   <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
     <t>example</t>
   </si>
   <si>
@@ -723,6 +735,9 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/device-kind|4.0.1</t>
+  </si>
+  <si>
+    <t>CD</t>
   </si>
   <si>
     <t>DeviceDefinition.specialization</t>
@@ -811,9 +826,6 @@
     <t>DeviceDefinition.physicalCharacteristics.extension</t>
   </si>
   <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
     <t>DeviceDefinition.physicalCharacteristics.extension:InternalDiameter</t>
   </si>
   <si>
@@ -846,7 +858,17 @@
     <t>Where applicable, the height can be specified using a numerical value and its unit of measurement The unit of measurement shall be specified in accordance with ISO 11240 and the resulting terminology The symbol and the symbol identifier shall be used.</t>
   </si>
   <si>
+    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
+  </si>
+  <si>
     <t>ProdCharacteristic.height</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}</t>
+  </si>
+  <si>
+    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
   </si>
   <si>
     <t>DeviceDefinition.physicalCharacteristics.width</t>
@@ -958,7 +980,17 @@
     <t>Where applicable, the image can be provided The format of the image attachment shall be specified by regional implementations.</t>
   </si>
   <si>
+    <t>When providing a summary view (for example with Observation.value[x]) Attachment should be represented with a brief display text such as "Signed Procedure Consent".</t>
+  </si>
+  <si>
     <t>ProdCharacteristic.image</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+att-1:If the Attachment has data, it SHALL have a contentType {data.empty() or contentType.exists()}</t>
+  </si>
+  <si>
+    <t>ED</t>
   </si>
   <si>
     <t>DeviceDefinition.physicalCharacteristics.scoring</t>
@@ -1272,6 +1304,13 @@
     <t>An organization that is responsible for the provision and ongoing maintenance of the device.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
     <t>FiveWs.source</t>
   </si>
   <si>
@@ -1294,6 +1333,10 @@
     <t>used for troubleshooting etc.</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}</t>
+  </si>
+  <si>
     <t>.scopedRole[typeCode=CON].player</t>
   </si>
   <si>
@@ -1337,6 +1380,9 @@
     <t>Descriptive information, usage information or implantation information that is not captured in an existing element.</t>
   </si>
   <si>
+    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
+  </si>
+  <si>
     <t>.text</t>
   </si>
   <si>
@@ -1360,6 +1406,9 @@
   </si>
   <si>
     <t>The parent device it can be part of.</t>
+  </si>
+  <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
   </si>
   <si>
     <t>DeviceDefinition.material</t>
@@ -1749,7 +1798,7 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="35.69140625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="123.23828125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2178,24 +2227,24 @@
         <v>85</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2218,16 +2267,16 @@
         <v>86</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2277,7 +2326,7 @@
         <v>75</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>76</v>
@@ -2286,24 +2335,24 @@
         <v>85</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2326,16 +2375,16 @@
         <v>75</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2361,13 +2410,13 @@
         <v>75</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>75</v>
@@ -2385,7 +2434,7 @@
         <v>75</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>76</v>
@@ -2394,28 +2443,28 @@
         <v>85</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2434,16 +2483,16 @@
         <v>75</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2493,7 +2542,7 @@
         <v>75</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
@@ -2502,28 +2551,28 @@
         <v>85</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2542,16 +2591,16 @@
         <v>75</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2601,7 +2650,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>76</v>
@@ -2619,19 +2668,19 @@
         <v>75</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2650,15 +2699,17 @@
         <v>75</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>135</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>75</v>
@@ -2695,17 +2746,19 @@
         <v>75</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
@@ -2714,27 +2767,27 @@
         <v>77</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>75</v>
@@ -2756,13 +2809,13 @@
         <v>75</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2813,7 +2866,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -2822,10 +2875,10 @@
         <v>77</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>75</v>
@@ -2836,13 +2889,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>75</v>
@@ -2864,13 +2917,13 @@
         <v>75</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2921,7 +2974,7 @@
         <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
@@ -2930,10 +2983,10 @@
         <v>77</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>75</v>
@@ -2944,13 +2997,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>75</v>
@@ -2972,13 +3025,13 @@
         <v>75</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3029,7 +3082,7 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -3038,10 +3091,10 @@
         <v>77</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>75</v>
@@ -3052,14 +3105,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3078,19 +3131,19 @@
         <v>75</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>75</v>
@@ -3127,19 +3180,19 @@
         <v>75</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -3148,24 +3201,24 @@
         <v>77</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3188,13 +3241,13 @@
         <v>75</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3245,7 +3298,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -3254,24 +3307,24 @@
         <v>77</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>75</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3294,13 +3347,13 @@
         <v>75</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3351,7 +3404,7 @@
         <v>75</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -3360,24 +3413,24 @@
         <v>77</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3400,13 +3453,13 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3457,7 +3510,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -3475,19 +3528,19 @@
         <v>75</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>174</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3506,16 +3559,16 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3553,19 +3606,19 @@
         <v>75</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3574,28 +3627,28 @@
         <v>77</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>174</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3614,19 +3667,19 @@
         <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>75</v>
@@ -3675,7 +3728,7 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3684,24 +3737,24 @@
         <v>77</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3724,15 +3777,17 @@
         <v>75</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>75</v>
@@ -3781,7 +3836,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>85</v>
@@ -3790,24 +3845,24 @@
         <v>85</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3830,15 +3885,17 @@
         <v>75</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>75</v>
@@ -3887,7 +3944,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>85</v>
@@ -3896,24 +3953,24 @@
         <v>85</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3936,15 +3993,17 @@
         <v>75</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="M21" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>75</v>
@@ -3993,7 +4052,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>85</v>
@@ -4002,24 +4061,24 @@
         <v>85</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4042,13 +4101,13 @@
         <v>75</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4099,7 +4158,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -4108,24 +4167,24 @@
         <v>85</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4148,13 +4207,13 @@
         <v>75</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4205,7 +4264,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -4214,24 +4273,24 @@
         <v>77</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4254,13 +4313,13 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4311,7 +4370,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -4329,19 +4388,19 @@
         <v>75</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>174</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4360,16 +4419,16 @@
         <v>75</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4407,19 +4466,19 @@
         <v>75</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4428,28 +4487,28 @@
         <v>77</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>174</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4468,19 +4527,19 @@
         <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>75</v>
@@ -4529,7 +4588,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -4538,28 +4597,28 @@
         <v>77</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4578,15 +4637,17 @@
         <v>75</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>75</v>
@@ -4635,7 +4696,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>85</v>
@@ -4644,24 +4705,24 @@
         <v>85</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4684,15 +4745,17 @@
         <v>75</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>75</v>
@@ -4717,31 +4780,31 @@
         <v>75</v>
       </c>
       <c r="X28" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>85</v>
@@ -4750,24 +4813,24 @@
         <v>85</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4790,15 +4853,17 @@
         <v>75</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>75</v>
@@ -4847,7 +4912,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4856,24 +4921,24 @@
         <v>85</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4896,15 +4961,17 @@
         <v>75</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>75</v>
@@ -4929,13 +4996,13 @@
         <v>75</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>75</v>
@@ -4953,7 +5020,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4962,24 +5029,24 @@
         <v>85</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5002,13 +5069,13 @@
         <v>75</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5059,7 +5126,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -5068,24 +5135,24 @@
         <v>77</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5108,13 +5175,13 @@
         <v>75</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5165,7 +5232,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -5183,19 +5250,19 @@
         <v>75</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>174</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5214,16 +5281,16 @@
         <v>75</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5261,19 +5328,19 @@
         <v>75</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -5282,28 +5349,28 @@
         <v>77</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>174</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5322,19 +5389,19 @@
         <v>86</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>75</v>
@@ -5383,7 +5450,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5392,28 +5459,28 @@
         <v>77</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5432,15 +5499,17 @@
         <v>75</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>75</v>
@@ -5489,7 +5558,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>85</v>
@@ -5498,24 +5567,24 @@
         <v>85</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5538,15 +5607,17 @@
         <v>75</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>75</v>
@@ -5595,7 +5666,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5604,24 +5675,24 @@
         <v>85</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5644,15 +5715,17 @@
         <v>75</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>246</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>75</v>
@@ -5701,7 +5774,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5710,24 +5783,24 @@
         <v>77</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5750,15 +5823,17 @@
         <v>86</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>75</v>
@@ -5783,11 +5858,11 @@
         <v>75</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>75</v>
@@ -5805,7 +5880,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5814,24 +5889,24 @@
         <v>77</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5854,13 +5929,13 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5911,7 +5986,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5920,24 +5995,24 @@
         <v>77</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5960,13 +6035,13 @@
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6017,7 +6092,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -6026,24 +6101,24 @@
         <v>85</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6066,13 +6141,13 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6123,7 +6198,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -6141,19 +6216,19 @@
         <v>75</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>174</v>
+        <v>106</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6172,16 +6247,16 @@
         <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6219,19 +6294,19 @@
         <v>75</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>255</v>
+        <v>138</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -6240,27 +6315,27 @@
         <v>77</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>174</v>
+        <v>99</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>75</v>
@@ -6282,13 +6357,13 @@
         <v>75</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6339,7 +6414,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6348,10 +6423,10 @@
         <v>77</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>75</v>
@@ -6362,14 +6437,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6388,19 +6463,19 @@
         <v>86</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>75</v>
@@ -6449,7 +6524,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6458,24 +6533,24 @@
         <v>77</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6498,15 +6573,17 @@
         <v>86</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>75</v>
@@ -6555,7 +6632,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6564,24 +6641,24 @@
         <v>85</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6604,15 +6681,17 @@
         <v>86</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>75</v>
@@ -6661,7 +6740,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6670,24 +6749,24 @@
         <v>85</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6710,15 +6789,17 @@
         <v>86</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>75</v>
@@ -6767,7 +6848,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6776,24 +6857,24 @@
         <v>85</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6816,15 +6897,17 @@
         <v>86</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>75</v>
@@ -6873,7 +6956,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -6882,24 +6965,24 @@
         <v>85</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6922,15 +7005,17 @@
         <v>86</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>75</v>
@@ -6979,7 +7064,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -6988,24 +7073,24 @@
         <v>85</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7028,15 +7113,17 @@
         <v>86</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>75</v>
@@ -7085,7 +7172,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7094,24 +7181,24 @@
         <v>85</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7134,15 +7221,17 @@
         <v>86</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>75</v>
@@ -7191,7 +7280,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7200,24 +7289,24 @@
         <v>85</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7240,15 +7329,17 @@
         <v>86</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>75</v>
@@ -7297,7 +7388,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7306,24 +7397,24 @@
         <v>77</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7346,15 +7437,17 @@
         <v>86</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>75</v>
@@ -7403,7 +7496,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7412,24 +7505,24 @@
         <v>77</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7452,15 +7545,17 @@
         <v>86</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>75</v>
@@ -7509,7 +7604,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7518,24 +7613,24 @@
         <v>77</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>97</v>
+        <v>312</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>75</v>
+        <v>313</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7558,15 +7653,17 @@
         <v>86</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>75</v>
@@ -7615,7 +7712,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -7624,24 +7721,24 @@
         <v>85</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7664,15 +7761,17 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>75</v>
@@ -7721,7 +7820,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -7730,24 +7829,24 @@
         <v>77</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7770,13 +7869,13 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7827,7 +7926,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -7836,24 +7935,24 @@
         <v>77</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7876,13 +7975,13 @@
         <v>75</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7933,7 +8032,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -7951,19 +8050,19 @@
         <v>75</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>174</v>
+        <v>106</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -7982,16 +8081,16 @@
         <v>75</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8029,19 +8128,19 @@
         <v>75</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -8050,28 +8149,28 @@
         <v>77</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>174</v>
+        <v>99</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8090,19 +8189,19 @@
         <v>86</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>75</v>
@@ -8151,7 +8250,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8160,24 +8259,24 @@
         <v>77</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8200,15 +8299,17 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>75</v>
@@ -8257,7 +8358,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>85</v>
@@ -8266,24 +8367,24 @@
         <v>85</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8306,15 +8407,17 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>332</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>75</v>
@@ -8363,7 +8466,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -8372,24 +8475,24 @@
         <v>77</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8412,13 +8515,13 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8457,17 +8560,17 @@
         <v>75</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="AC63" s="2"/>
       <c r="AD63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -8476,24 +8579,24 @@
         <v>77</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8516,13 +8619,13 @@
         <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8573,7 +8676,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -8591,19 +8694,19 @@
         <v>75</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>174</v>
+        <v>106</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8622,16 +8725,16 @@
         <v>75</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8669,19 +8772,19 @@
         <v>75</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -8690,28 +8793,28 @@
         <v>77</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>174</v>
+        <v>99</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -8730,19 +8833,19 @@
         <v>86</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>75</v>
@@ -8791,7 +8894,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -8800,24 +8903,24 @@
         <v>77</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8840,15 +8943,17 @@
         <v>75</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>75</v>
@@ -8897,7 +9002,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>85</v>
@@ -8906,24 +9011,24 @@
         <v>85</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8946,15 +9051,17 @@
         <v>75</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>75</v>
@@ -9003,7 +9110,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -9012,24 +9119,24 @@
         <v>77</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9052,15 +9159,17 @@
         <v>75</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>75</v>
@@ -9109,7 +9218,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9118,27 +9227,27 @@
         <v>77</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="D70" t="s" s="2">
         <v>75</v>
@@ -9160,13 +9269,13 @@
         <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9217,7 +9326,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -9226,24 +9335,24 @@
         <v>77</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9266,13 +9375,13 @@
         <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9323,7 +9432,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -9341,19 +9450,19 @@
         <v>75</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>174</v>
+        <v>106</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -9372,16 +9481,16 @@
         <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9419,19 +9528,19 @@
         <v>75</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -9440,28 +9549,28 @@
         <v>77</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>174</v>
+        <v>99</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -9480,19 +9589,19 @@
         <v>86</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>75</v>
@@ -9541,7 +9650,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -9550,24 +9659,24 @@
         <v>77</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9590,15 +9699,17 @@
         <v>75</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>75</v>
@@ -9608,7 +9719,7 @@
         <v>75</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>75</v>
@@ -9647,7 +9758,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>85</v>
@@ -9656,24 +9767,24 @@
         <v>85</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9696,15 +9807,17 @@
         <v>75</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>75</v>
@@ -9753,7 +9866,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -9762,24 +9875,24 @@
         <v>77</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9802,15 +9915,17 @@
         <v>75</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>75</v>
@@ -9859,7 +9974,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -9868,27 +9983,27 @@
         <v>77</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>75</v>
@@ -9910,13 +10025,13 @@
         <v>75</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -9967,7 +10082,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -9976,24 +10091,24 @@
         <v>77</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10016,13 +10131,13 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10073,7 +10188,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -10091,19 +10206,19 @@
         <v>75</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>174</v>
+        <v>106</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -10122,16 +10237,16 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10169,19 +10284,19 @@
         <v>75</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -10190,28 +10305,28 @@
         <v>77</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>174</v>
+        <v>99</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -10230,19 +10345,19 @@
         <v>86</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>75</v>
@@ -10291,7 +10406,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -10300,24 +10415,24 @@
         <v>77</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10340,15 +10455,17 @@
         <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>75</v>
@@ -10358,7 +10475,7 @@
         <v>75</v>
       </c>
       <c r="S81" t="s" s="2">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="T81" t="s" s="2">
         <v>75</v>
@@ -10397,7 +10514,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>85</v>
@@ -10406,24 +10523,24 @@
         <v>85</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10446,15 +10563,17 @@
         <v>75</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>75</v>
@@ -10503,7 +10622,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -10512,24 +10631,24 @@
         <v>77</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10552,15 +10671,17 @@
         <v>75</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>75</v>
@@ -10609,7 +10730,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -10618,27 +10739,27 @@
         <v>77</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>75</v>
@@ -10660,13 +10781,13 @@
         <v>75</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -10717,7 +10838,7 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -10726,24 +10847,24 @@
         <v>77</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10766,13 +10887,13 @@
         <v>75</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -10823,7 +10944,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -10841,19 +10962,19 @@
         <v>75</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>174</v>
+        <v>106</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -10872,16 +10993,16 @@
         <v>75</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -10919,19 +11040,19 @@
         <v>75</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
@@ -10940,28 +11061,28 @@
         <v>77</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>174</v>
+        <v>99</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -10980,19 +11101,19 @@
         <v>86</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>75</v>
@@ -11041,7 +11162,7 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
@@ -11050,24 +11171,24 @@
         <v>77</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11090,15 +11211,17 @@
         <v>75</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N88" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>75</v>
@@ -11108,7 +11231,7 @@
         <v>75</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>75</v>
@@ -11147,7 +11270,7 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>85</v>
@@ -11156,24 +11279,24 @@
         <v>85</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11196,15 +11319,17 @@
         <v>75</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N89" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>75</v>
@@ -11253,7 +11378,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
@@ -11262,24 +11387,24 @@
         <v>77</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11302,15 +11427,17 @@
         <v>75</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>75</v>
@@ -11359,7 +11486,7 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -11368,27 +11495,27 @@
         <v>77</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="D91" t="s" s="2">
         <v>75</v>
@@ -11410,13 +11537,13 @@
         <v>75</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -11467,7 +11594,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
@@ -11476,24 +11603,24 @@
         <v>77</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11516,13 +11643,13 @@
         <v>75</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -11573,7 +11700,7 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -11591,19 +11718,19 @@
         <v>75</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>174</v>
+        <v>106</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -11622,16 +11749,16 @@
         <v>75</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -11669,19 +11796,19 @@
         <v>75</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -11690,28 +11817,28 @@
         <v>77</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>174</v>
+        <v>99</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -11730,19 +11857,19 @@
         <v>86</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>75</v>
@@ -11791,7 +11918,7 @@
         <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
@@ -11800,24 +11927,24 @@
         <v>77</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11840,15 +11967,17 @@
         <v>75</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>75</v>
@@ -11858,7 +11987,7 @@
         <v>75</v>
       </c>
       <c r="S95" t="s" s="2">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="T95" t="s" s="2">
         <v>75</v>
@@ -11897,7 +12026,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>85</v>
@@ -11906,24 +12035,24 @@
         <v>85</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11946,15 +12075,17 @@
         <v>75</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N96" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>75</v>
@@ -12003,7 +12134,7 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>76</v>
@@ -12012,24 +12143,24 @@
         <v>77</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12052,15 +12183,17 @@
         <v>75</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N97" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>75</v>
@@ -12109,7 +12242,7 @@
         <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>76</v>
@@ -12118,27 +12251,27 @@
         <v>77</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>75</v>
@@ -12160,13 +12293,13 @@
         <v>75</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -12217,7 +12350,7 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>
@@ -12226,24 +12359,24 @@
         <v>77</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12266,13 +12399,13 @@
         <v>75</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -12323,7 +12456,7 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
@@ -12341,19 +12474,19 @@
         <v>75</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>174</v>
+        <v>106</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -12372,16 +12505,16 @@
         <v>75</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -12419,19 +12552,19 @@
         <v>75</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="AC100" t="s" s="2">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="AD100" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>76</v>
@@ -12440,28 +12573,28 @@
         <v>77</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>174</v>
+        <v>99</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -12480,19 +12613,19 @@
         <v>86</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>75</v>
@@ -12541,7 +12674,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>76</v>
@@ -12550,24 +12683,24 @@
         <v>77</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12590,15 +12723,17 @@
         <v>75</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N102" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>75</v>
@@ -12608,7 +12743,7 @@
         <v>75</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="T102" t="s" s="2">
         <v>75</v>
@@ -12647,7 +12782,7 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>85</v>
@@ -12656,24 +12791,24 @@
         <v>85</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12696,15 +12831,17 @@
         <v>75</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>75</v>
@@ -12753,7 +12890,7 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>76</v>
@@ -12762,24 +12899,24 @@
         <v>77</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12802,15 +12939,17 @@
         <v>75</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N104" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>75</v>
@@ -12859,7 +12998,7 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>76</v>
@@ -12868,27 +13007,27 @@
         <v>77</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>75</v>
@@ -12910,13 +13049,13 @@
         <v>75</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -12967,7 +13106,7 @@
         <v>75</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>76</v>
@@ -12976,24 +13115,24 @@
         <v>77</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13016,13 +13155,13 @@
         <v>75</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -13073,7 +13212,7 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>76</v>
@@ -13091,19 +13230,19 @@
         <v>75</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>174</v>
+        <v>106</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -13122,16 +13261,16 @@
         <v>75</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -13169,19 +13308,19 @@
         <v>75</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>76</v>
@@ -13190,28 +13329,28 @@
         <v>77</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>174</v>
+        <v>99</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -13230,19 +13369,19 @@
         <v>86</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>75</v>
@@ -13291,7 +13430,7 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>76</v>
@@ -13300,24 +13439,24 @@
         <v>77</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13340,15 +13479,17 @@
         <v>75</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N109" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>75</v>
@@ -13358,7 +13499,7 @@
         <v>75</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>75</v>
@@ -13397,7 +13538,7 @@
         <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>85</v>
@@ -13406,24 +13547,24 @@
         <v>85</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13446,15 +13587,17 @@
         <v>75</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N110" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>75</v>
@@ -13503,7 +13646,7 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>76</v>
@@ -13512,24 +13655,24 @@
         <v>77</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13552,15 +13695,17 @@
         <v>75</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N111" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>75</v>
@@ -13609,7 +13754,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>76</v>
@@ -13618,24 +13763,24 @@
         <v>77</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13658,15 +13803,17 @@
         <v>75</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N112" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>75</v>
@@ -13715,7 +13862,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>76</v>
@@ -13724,24 +13871,24 @@
         <v>85</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>97</v>
+        <v>408</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>398</v>
+        <v>410</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13764,16 +13911,16 @@
         <v>75</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -13823,7 +13970,7 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>76</v>
@@ -13832,24 +13979,24 @@
         <v>77</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>97</v>
+        <v>416</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>404</v>
+        <v>417</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13872,16 +14019,16 @@
         <v>75</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -13931,7 +14078,7 @@
         <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
@@ -13940,24 +14087,24 @@
         <v>85</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>410</v>
+        <v>423</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13980,15 +14127,17 @@
         <v>75</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N115" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>75</v>
@@ -14037,7 +14186,7 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>76</v>
@@ -14046,24 +14195,24 @@
         <v>85</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14086,15 +14235,17 @@
         <v>75</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N116" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>431</v>
+      </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>75</v>
@@ -14143,7 +14294,7 @@
         <v>75</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>76</v>
@@ -14152,24 +14303,24 @@
         <v>77</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>418</v>
+        <v>432</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14192,15 +14343,17 @@
         <v>75</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N117" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>75</v>
@@ -14249,7 +14402,7 @@
         <v>75</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>76</v>
@@ -14258,24 +14411,24 @@
         <v>85</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14298,15 +14451,17 @@
         <v>86</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N118" s="2"/>
+        <v>439</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>75</v>
@@ -14355,7 +14510,7 @@
         <v>75</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>76</v>
@@ -14364,24 +14519,24 @@
         <v>85</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>97</v>
+        <v>408</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>75</v>
+        <v>440</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14404,13 +14559,13 @@
         <v>75</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -14461,7 +14616,7 @@
         <v>75</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>76</v>
@@ -14470,24 +14625,24 @@
         <v>77</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14510,13 +14665,13 @@
         <v>75</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -14567,7 +14722,7 @@
         <v>75</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>76</v>
@@ -14585,19 +14740,19 @@
         <v>75</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>174</v>
+        <v>106</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
@@ -14616,16 +14771,16 @@
         <v>75</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -14663,19 +14818,19 @@
         <v>75</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>76</v>
@@ -14684,28 +14839,28 @@
         <v>77</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>174</v>
+        <v>99</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>431</v>
+        <v>446</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>431</v>
+        <v>446</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -14724,19 +14879,19 @@
         <v>86</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>75</v>
@@ -14785,7 +14940,7 @@
         <v>75</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>76</v>
@@ -14794,24 +14949,24 @@
         <v>77</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14834,15 +14989,17 @@
         <v>75</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N123" s="2"/>
+        <v>449</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>75</v>
@@ -14891,7 +15048,7 @@
         <v>75</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>85</v>
@@ -14900,24 +15057,24 @@
         <v>85</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14940,13 +15097,13 @@
         <v>75</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -14997,7 +15154,7 @@
         <v>75</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>76</v>
@@ -15006,24 +15163,24 @@
         <v>85</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15046,13 +15203,13 @@
         <v>75</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -15103,7 +15260,7 @@
         <v>75</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>76</v>
@@ -15112,16 +15269,16 @@
         <v>85</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
